--- a/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Metalworking.xlsx
+++ b/output/2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Metalworking.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Confermata sezione catalogo 'Industrijski Sesalniki' con 26 prodotti a listino. Azienda familiare fondata nel 2017.</t>
+          <t>Confermata sezione catalogo 'Industrijski Sesalniki' con 26 prodotti a listino. Azienda familiare fondata nel 2017. [DUPLICATO — vedi anche: 2026-09-05_21_Slovenia_Pomurska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
